--- a/rtl/pll_register_file.xlsx
+++ b/rtl/pll_register_file.xlsx
@@ -1039,8 +1039,10 @@
       <x:c r="D43" s="5" t="str"/>
       <x:c r="E43" s="5" t="str"/>
       <x:c r="F43" s="5" t="str"/>
-      <x:c r="G43" s="5" t="str">
-        <x:v>独立配置UART：25 MHz / 115200 bps / 8N1。原业务UART协议不变。</x:v>
+      <x:c r="G43" s="5" t="inlineStr">
+        <x:is>
+          <x:t>独立配置UART：25 MHz / 1 Mbps / 8N1。原业务UART协议不变。</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="44" ht="48" customHeight="1">
@@ -1169,8 +1171,10 @@
       <x:c r="F53" s="5" t="str">
         <x:v>内部旁路配置</x:v>
       </x:c>
-      <x:c r="G53" s="5" t="str">
-        <x:v>先写01 00 0A 20，再APPLY。正常完成STATUS=0x007A；业务UART匹配625 kbps。</x:v>
+      <x:c r="G53" s="5" t="inlineStr">
+        <x:is>
+          <x:t>先写01 00 0A 20，再APPLY。正常完成STATUS=0x007A；业务UART匹配62.5 kbps。</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="54" ht="48" customHeight="1">
@@ -1182,8 +1186,10 @@
       <x:c r="F54" s="5" t="str">
         <x:v>启动与业务UART</x:v>
       </x:c>
-      <x:c r="G54" s="5" t="str">
-        <x:v>上电需APPLY。400 MHz业务UART为10 Mbps；配置UART始终115200 bps。</x:v>
+      <x:c r="G54" s="5" t="inlineStr">
+        <x:is>
+          <x:t>上电需APPLY。400 MHz业务UART为1 Mbps；配置UART始终1 Mbps。</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="55" ht="32" customHeight="1">
